--- a/J30/Output_files/iLPN_Information_Results.xlsx
+++ b/J30/Output_files/iLPN_Information_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,18 +504,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00V09112025QA23602</t>
+          <t>00V09172025QA13202</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0911QA4410</t>
+          <t>VGASN0917QA2960</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,11 +525,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>829748-010-XS</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -564,18 +564,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00V09112025QA44001</t>
+          <t>00V09172025QA20600</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0911QA4410</t>
+          <t>VGASN0917QA2960</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -585,11 +585,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>829748-010-XS</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -624,18 +624,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00V09112025QA98300</t>
+          <t>00V09172025QA30401</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0911QA4410</t>
+          <t>VGASN0917QA2960</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FIRST_SKU</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,11 +645,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>829748-010-XS</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -676,6 +676,66 @@
         </is>
       </c>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>25050501</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00V09172025QA37303</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN0917QA2960</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>25050501</t>
         </is>
@@ -707,7 +767,7 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-09-11T19:09:29.591",
+    "CreatedTimestamp": "2025-09-18T01:09:57.94",
     "VolumeUomId": null,
     "PhysicalEntityCodeId": null,
     "FinalDestinationFacilityId": null,
@@ -719,7 +779,7 @@
         "DestinationFacilityId": null,
         "LpnWidth": 12.0
     },
-    "DiversionCodeId": "FIRST_SKU",
+    "DiversionCodeId": "IN_VAS",
     "Process": "ReceivingLpnService",
     "ItemAttributesValidated": true,
     "UpdatedBy": "vgana3",
@@ -730,15 +790,15 @@
     "Width": null,
     "LpnSizeTypeId": "CARTON",
     "Asn": {
-        "AsnId": "VGASN0911QA4410"
+        "AsnId": "VGASN0917QA2960"
     },
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN0911QA4410",
-    "UpdatedTimestamp": "2025-09-11T19:21:31.517",
+    "AsnId": "VGASN0917QA2960",
+    "UpdatedTimestamp": "2025-09-18T01:18:10.109",
     "MarkFor": null,
     "CreatedBy": "vgana3",
     "ParentLpnId": null,
-    "LpnId": "00V09112025QA98300",
+    "LpnId": "00V09172025QA37303",
     "AllocationTypeId": "ProcessNeed And Sorting",
     "BusinessUnitId": null,
     "LpnStatus": "4000",
@@ -749,7 +809,7 @@
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-09-11T19:09:29.592",
+            "CreatedTimestamp": "2025-09-18T01:09:57.941",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -760,7 +820,7 @@
             "Process": "PreReceiptResponseProcessingService",
             "AsnLineId": null,
             "InventoryTypeId": null,
-            "ItemId": "829748-010-XS",
+            "ItemId": "DD9293-100-7",
             "UpdatedBy": "vgana3",
             "InventoryAttribute1": "01000",
             "InventoryAttribute2": null,
@@ -775,15 +835,15 @@
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
             "PurchaseOrderId": "25050501",
-            "ContextId": "f7ad7069d492b7e6::b4dbf87303ec2760",
-            "LpnDetailId": "6e9684cd-0805-4436-b82f-76c8ce09b301",
+            "ContextId": "0e24d10d61bb2da6::2389701fa39e0711",
+            "LpnDetailId": "35b61338-a1bb-4a2a-afe7-3d4ca03f2266",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7576177695917631543
+                "PK": 7581577979406498817
             },
             "QuantityUomId": "LPN",
             "SeasonYear": null,
@@ -795,18 +855,18 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-09-11T19:11:21.095",
+            "UpdatedTimestamp": "2025-09-18T01:15:22.083",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
-            "ShippedQuantity": 2.0,
+            "ShippedQuantity": 6.0,
             "AlternatePurchaseOrderId": null,
             "EntityLabels": null,
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7576177695927642009",
-            "Unique_Identifier": "7576177695927642009__6e9684cd-0805-4436-b82f-76c8ce09b301"
+            "PK": "7581577979416501264",
+            "Unique_Identifier": "7581577979416501264__35b61338-a1bb-4a2a-afe7-3d4ca03f2266"
         }
     ],
     "EntityLabels": null,
@@ -818,10 +878,10 @@
     "PreReceiptStatusId": "4",
     "SingleItemLpn": true,
     "PurchaseOrderId": "25050501",
-    "ContextId": "0355dc6928748657::910df4a5c5252be7",
+    "ContextId": "382b1ff8de6890d5::a1ece5167bd22374",
     "Canceled": false,
-    "PK": "7576177695917631543",
-    "Unique_Identifier": "7576177695917631543__00V09112025QA98300",
+    "PK": "7581577979406498817",
+    "Unique_Identifier": "7581577979406498817__00V09172025QA37303",
     "DimensionUomId": null,
     "EstimationGroupId": null
 }</t>

--- a/J30/Output_files/iLPN_Information_Results.xlsx
+++ b/J30/Output_files/iLPN_Information_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,13 +504,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00V09172025QA13202</t>
+          <t>00V09252025QA2143804</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0917QA2960</t>
+          <t>VGASN0925QA1650</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>DD9293-100-6</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -564,13 +564,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00V09172025QA20600</t>
+          <t>00V09252025QA2177800</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0917QA2960</t>
+          <t>VGASN0925QA1650</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>829748-010-4XL</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -624,18 +624,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00V09172025QA30401</t>
+          <t>00V09252025QA4433802</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0917QA2960</t>
+          <t>VGASN0925QA1650</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IN_VAS</t>
+          <t>MIXED_SKU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -684,18 +684,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00V09172025QA37303</t>
+          <t>00V09252025QA4433802</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN0917QA2960</t>
+          <t>VGASN0925QA1650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IN_VAS</t>
+          <t>MIXED_SKU</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>DD9293-100-6</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -736,6 +736,246 @@
         </is>
       </c>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>25050501</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00V09252025QA6642501</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN0925QA1650</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>829748-010-4XL</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>24</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>25050501</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00V09252025QA7767403</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN0925QA1650</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>24</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>25050501</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00V09252025QA7767403</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN0925QA1650</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DD9293-100-6</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>24</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>12</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>25050501</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00V09252025QA8703705</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN0925QA1650</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DD9293-100-6</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>25050501</t>
         </is>
@@ -767,7 +1007,7 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-09-18T01:09:57.94",
+    "CreatedTimestamp": "2025-09-25T15:55:17.765",
     "VolumeUomId": null,
     "PhysicalEntityCodeId": null,
     "FinalDestinationFacilityId": null,
@@ -779,7 +1019,7 @@
         "DestinationFacilityId": null,
         "LpnWidth": 12.0
     },
-    "DiversionCodeId": "IN_VAS",
+    "DiversionCodeId": "STORAGE",
     "Process": "ReceivingLpnService",
     "ItemAttributesValidated": true,
     "UpdatedBy": "vgana3",
@@ -790,15 +1030,15 @@
     "Width": null,
     "LpnSizeTypeId": "CARTON",
     "Asn": {
-        "AsnId": "VGASN0917QA2960"
+        "AsnId": "VGASN0925QA1650"
     },
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN0917QA2960",
-    "UpdatedTimestamp": "2025-09-18T01:18:10.109",
+    "AsnId": "VGASN0925QA1650",
+    "UpdatedTimestamp": "2025-09-25T16:02:29.073",
     "MarkFor": null,
     "CreatedBy": "vgana3",
     "ParentLpnId": null,
-    "LpnId": "00V09172025QA37303",
+    "LpnId": "00V09252025QA8703705",
     "AllocationTypeId": "ProcessNeed And Sorting",
     "BusinessUnitId": null,
     "LpnStatus": "4000",
@@ -809,7 +1049,7 @@
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-09-18T01:09:57.941",
+            "CreatedTimestamp": "2025-09-25T15:55:17.767",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -820,7 +1060,7 @@
             "Process": "PreReceiptResponseProcessingService",
             "AsnLineId": null,
             "InventoryTypeId": null,
-            "ItemId": "DD9293-100-7",
+            "ItemId": "DD9293-100-6",
             "UpdatedBy": "vgana3",
             "InventoryAttribute1": "01000",
             "InventoryAttribute2": null,
@@ -835,15 +1075,15 @@
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
             "PurchaseOrderId": "25050501",
-            "ContextId": "0e24d10d61bb2da6::2389701fa39e0711",
-            "LpnDetailId": "35b61338-a1bb-4a2a-afe7-3d4ca03f2266",
+            "ContextId": "b6f5fa5e2aee9227::67be4120b8a8765f",
+            "LpnDetailId": "6267e00e-0b4a-40d7-8b08-56f08d278520",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7581577979406498817
+                "PK": 7588157177651378276
             },
             "QuantityUomId": "LPN",
             "SeasonYear": null,
@@ -855,7 +1095,7 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-09-18T01:15:22.083",
+            "UpdatedTimestamp": "2025-09-25T15:59:28.995",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
@@ -865,8 +1105,8 @@
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7581577979416501264",
-            "Unique_Identifier": "7581577979416501264__35b61338-a1bb-4a2a-afe7-3d4ca03f2266"
+            "PK": "7588157177671383787",
+            "Unique_Identifier": "7588157177671383787__6267e00e-0b4a-40d7-8b08-56f08d278520"
         }
     ],
     "EntityLabels": null,
@@ -878,10 +1118,10 @@
     "PreReceiptStatusId": "4",
     "SingleItemLpn": true,
     "PurchaseOrderId": "25050501",
-    "ContextId": "382b1ff8de6890d5::a1ece5167bd22374",
+    "ContextId": "99167fc1ddeb49c6::f97d01f508bd9da0",
     "Canceled": false,
-    "PK": "7581577979406498817",
-    "Unique_Identifier": "7581577979406498817__00V09172025QA37303",
+    "PK": "7588157177651378276",
+    "Unique_Identifier": "7588157177651378276__00V09252025QA8703705",
     "DimensionUomId": null,
     "EstimationGroupId": null
 }</t>

--- a/J30/Output_files/iLPN_Information_Results.xlsx
+++ b/J30/Output_files/iLPN_Information_Results.xlsx
@@ -504,18 +504,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00V09252025QA2143804</t>
+          <t>00V10012025QA1736600</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0925QA1650</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IN_VAS</t>
+          <t>FIRST_SKU</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DD9293-100-6</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -557,25 +557,25 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>25050501</t>
+          <t>PO10011582</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00V09252025QA2177800</t>
+          <t>00V10012025QA2830407</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0925QA1650</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IN_VAS</t>
+          <t>STORAGE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>829748-010-4XL</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>25050501</t>
+          <t>PO10011582</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00V09252025QA4433802</t>
+          <t>00V10012025QA4537706</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0925QA1650</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -677,25 +677,25 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>25050501</t>
+          <t>PO10011582</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00V09252025QA4433802</t>
+          <t>00V10012025QA4796105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN0925QA1650</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>MEASUREMENT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DD9293-100-6</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -737,25 +737,25 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>25050501</t>
+          <t>PO10011582</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00V09252025QA6642501</t>
+          <t>00V10012025QA6786203</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VGASN0925QA1650</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>829748-010-4XL</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -797,25 +797,25 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>25050501</t>
+          <t>PO10011582</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00V09252025QA7767403</t>
+          <t>00V10012025QA7313704</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VGASN0925QA1650</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -857,25 +857,25 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>25050501</t>
+          <t>PO10011582</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00V09252025QA7767403</t>
+          <t>00V10012025QA7372301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VGASN0925QA1650</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DD9293-100-6</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -917,25 +917,25 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>25050501</t>
+          <t>PO10011582</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00V09252025QA8703705</t>
+          <t>00V10012025QA9183902</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VGASN0925QA1650</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DD9293-100-6</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -977,7 +977,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>25050501</t>
+          <t>PO10011582</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-09-25T15:55:17.765",
+    "CreatedTimestamp": "2025-10-01T21:03:28.173",
     "VolumeUomId": null,
     "PhysicalEntityCodeId": null,
     "FinalDestinationFacilityId": null,
@@ -1019,7 +1019,7 @@
         "DestinationFacilityId": null,
         "LpnWidth": 12.0
     },
-    "DiversionCodeId": "STORAGE",
+    "DiversionCodeId": "IN_VAS",
     "Process": "ReceivingLpnService",
     "ItemAttributesValidated": true,
     "UpdatedBy": "vgana3",
@@ -1030,15 +1030,15 @@
     "Width": null,
     "LpnSizeTypeId": "CARTON",
     "Asn": {
-        "AsnId": "VGASN0925QA1650"
+        "AsnId": "VGASN1001QA1100"
     },
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN0925QA1650",
-    "UpdatedTimestamp": "2025-09-25T16:02:29.073",
+    "AsnId": "VGASN1001QA1100",
+    "UpdatedTimestamp": "2025-10-01T21:10:47.443",
     "MarkFor": null,
     "CreatedBy": "vgana3",
     "ParentLpnId": null,
-    "LpnId": "00V09252025QA8703705",
+    "LpnId": "00V10012025QA9183902",
     "AllocationTypeId": "ProcessNeed And Sorting",
     "BusinessUnitId": null,
     "LpnStatus": "4000",
@@ -1049,7 +1049,7 @@
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-09-25T15:55:17.767",
+            "CreatedTimestamp": "2025-10-01T21:03:28.175",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -1060,7 +1060,7 @@
             "Process": "PreReceiptResponseProcessingService",
             "AsnLineId": null,
             "InventoryTypeId": null,
-            "ItemId": "DD9293-100-6",
+            "ItemId": "829747-091-3XL",
             "UpdatedBy": "vgana3",
             "InventoryAttribute1": "01000",
             "InventoryAttribute2": null,
@@ -1074,18 +1074,18 @@
             "BusinessUnitId": null,
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
-            "PurchaseOrderId": "25050501",
-            "ContextId": "b6f5fa5e2aee9227::67be4120b8a8765f",
-            "LpnDetailId": "6267e00e-0b4a-40d7-8b08-56f08d278520",
+            "PurchaseOrderId": "PO10011582",
+            "ContextId": "35b1f6b89271f036::c350e33c11f692f7",
+            "LpnDetailId": "9c2bd4f9-540e-4d8b-b113-e5ee23c0b645",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7588157177651378276
+                "PK": 7593526081732721979
             },
-            "QuantityUomId": "LPN",
+            "QuantityUomId": "Unit",
             "SeasonYear": null,
             "ManufacturingDate": null,
             "Style": null,
@@ -1095,7 +1095,7 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-09-25T15:59:28.995",
+            "UpdatedTimestamp": "2025-10-01T21:08:33.273",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
@@ -1105,8 +1105,8 @@
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7588157177671383787",
-            "Unique_Identifier": "7588157177671383787__6267e00e-0b4a-40d7-8b08-56f08d278520"
+            "PK": "7593526081742732083",
+            "Unique_Identifier": "7593526081742732083__9c2bd4f9-540e-4d8b-b113-e5ee23c0b645"
         }
     ],
     "EntityLabels": null,
@@ -1117,11 +1117,11 @@
     "Length": null,
     "PreReceiptStatusId": "4",
     "SingleItemLpn": true,
-    "PurchaseOrderId": "25050501",
-    "ContextId": "99167fc1ddeb49c6::f97d01f508bd9da0",
+    "PurchaseOrderId": "PO10011582",
+    "ContextId": "4cd3f919a986159c::6ff5c53b4a7fc3be",
     "Canceled": false,
-    "PK": "7588157177651378276",
-    "Unique_Identifier": "7588157177651378276__00V09252025QA8703705",
+    "PK": "7593526081732721979",
+    "Unique_Identifier": "7593526081732721979__00V10012025QA9183902",
     "DimensionUomId": null,
     "EstimationGroupId": null
 }</t>

--- a/J30/Output_files/iLPN_Information_Results.xlsx
+++ b/J30/Output_files/iLPN_Information_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,18 +504,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00V10012025QA1736600</t>
+          <t>00V10072025QA3758700</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1001QA1100</t>
+          <t>VGASN1007QA7240</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FIRST_SKU</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -557,427 +557,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO10011582</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>00V10012025QA2830407</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>24</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>PO10011582</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>00V10012025QA4537706</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>PO10011582</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00V10012025QA4796105</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MEASUREMENT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>24</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>PO10011582</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>00V10012025QA6786203</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>IN_VAS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>24</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>12</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>PO10011582</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>00V10012025QA7313704</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>IN_VAS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>24</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>PO10011582</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>00V10012025QA7372301</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IN_VAS</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>24</v>
-      </c>
-      <c r="J8" t="n">
-        <v>12</v>
-      </c>
-      <c r="K8" t="n">
-        <v>12</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>PO10011582</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>00V10012025QA9183902</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>IN_VAS</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>24</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12</v>
-      </c>
-      <c r="K9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>PO10011582</t>
+          <t>PO10077686</t>
         </is>
       </c>
     </row>
@@ -1007,7 +587,7 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-10-01T21:03:28.173",
+    "CreatedTimestamp": "2025-10-07T13:53:52.689",
     "VolumeUomId": null,
     "PhysicalEntityCodeId": null,
     "FinalDestinationFacilityId": null,
@@ -1030,15 +610,15 @@
     "Width": null,
     "LpnSizeTypeId": "CARTON",
     "Asn": {
-        "AsnId": "VGASN1001QA1100"
+        "AsnId": "VGASN1007QA7240"
     },
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN1001QA1100",
-    "UpdatedTimestamp": "2025-10-01T21:10:47.443",
+    "AsnId": "VGASN1007QA7240",
+    "UpdatedTimestamp": "2025-10-07T13:58:49.388",
     "MarkFor": null,
     "CreatedBy": "vgana3",
     "ParentLpnId": null,
-    "LpnId": "00V10012025QA9183902",
+    "LpnId": "00V10072025QA3758700",
     "AllocationTypeId": "ProcessNeed And Sorting",
     "BusinessUnitId": null,
     "LpnStatus": "4000",
@@ -1049,7 +629,7 @@
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-10-01T21:03:28.175",
+            "CreatedTimestamp": "2025-10-07T13:53:52.691",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -1074,16 +654,16 @@
             "BusinessUnitId": null,
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
-            "PurchaseOrderId": "PO10011582",
-            "ContextId": "35b1f6b89271f036::c350e33c11f692f7",
-            "LpnDetailId": "9c2bd4f9-540e-4d8b-b113-e5ee23c0b645",
+            "PurchaseOrderId": "PO10077686",
+            "ContextId": "8e6242789c961a30::2a010325e1d7345f",
+            "LpnDetailId": "f3bf349a-a5f5-4c38-bd7a-6b11f9b91dbc",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7593526081732721979
+                "PK": 7598452326897334256
             },
             "QuantityUomId": "Unit",
             "SeasonYear": null,
@@ -1095,7 +675,7 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-10-01T21:08:33.273",
+            "UpdatedTimestamp": "2025-10-07T13:57:25.587",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
@@ -1105,8 +685,8 @@
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7593526081742732083",
-            "Unique_Identifier": "7593526081742732083__9c2bd4f9-540e-4d8b-b113-e5ee23c0b645"
+            "PK": "7598452326917341956",
+            "Unique_Identifier": "7598452326917341956__f3bf349a-a5f5-4c38-bd7a-6b11f9b91dbc"
         }
     ],
     "EntityLabels": null,
@@ -1117,11 +697,11 @@
     "Length": null,
     "PreReceiptStatusId": "4",
     "SingleItemLpn": true,
-    "PurchaseOrderId": "PO10011582",
-    "ContextId": "4cd3f919a986159c::6ff5c53b4a7fc3be",
+    "PurchaseOrderId": "PO10077686",
+    "ContextId": "30a8670c04a1196c::8aea6e974a4148a6",
     "Canceled": false,
-    "PK": "7593526081732721979",
-    "Unique_Identifier": "7593526081732721979__00V10012025QA9183902",
+    "PK": "7598452326897334256",
+    "Unique_Identifier": "7598452326897334256__00V10072025QA3758700",
     "DimensionUomId": null,
     "EstimationGroupId": null
 }</t>

--- a/J30/Output_files/iLPN_Information_Results.xlsx
+++ b/J30/Output_files/iLPN_Information_Results.xlsx
@@ -504,13 +504,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00V10072025QA3758700</t>
+          <t>00V10232025QA5520800</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1007QA7240</t>
+          <t>VGASN1023QA3490</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>829747-091-3XL</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -557,7 +557,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO10077686</t>
+          <t>PO10237578</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-10-07T13:53:52.689",
+    "CreatedTimestamp": "2025-10-23T20:13:59.729",
     "VolumeUomId": null,
     "PhysicalEntityCodeId": null,
     "FinalDestinationFacilityId": null,
@@ -610,15 +610,15 @@
     "Width": null,
     "LpnSizeTypeId": "CARTON",
     "Asn": {
-        "AsnId": "VGASN1007QA7240"
+        "AsnId": "VGASN1023QA3490"
     },
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN1007QA7240",
-    "UpdatedTimestamp": "2025-10-07T13:58:49.388",
+    "AsnId": "VGASN1023QA3490",
+    "UpdatedTimestamp": "2025-10-23T20:29:54.3",
     "MarkFor": null,
     "CreatedBy": "vgana3",
     "ParentLpnId": null,
-    "LpnId": "00V10072025QA3758700",
+    "LpnId": "00V10232025QA5520800",
     "AllocationTypeId": "ProcessNeed And Sorting",
     "BusinessUnitId": null,
     "LpnStatus": "4000",
@@ -629,7 +629,7 @@
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-10-07T13:53:52.691",
+            "CreatedTimestamp": "2025-10-23T20:13:59.771",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -640,7 +640,7 @@
             "Process": "PreReceiptResponseProcessingService",
             "AsnLineId": null,
             "InventoryTypeId": null,
-            "ItemId": "829747-091-3XL",
+            "ItemId": "DD9293-100-7",
             "UpdatedBy": "vgana3",
             "InventoryAttribute1": "01000",
             "InventoryAttribute2": null,
@@ -654,16 +654,16 @@
             "BusinessUnitId": null,
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
-            "PurchaseOrderId": "PO10077686",
-            "ContextId": "8e6242789c961a30::2a010325e1d7345f",
-            "LpnDetailId": "f3bf349a-a5f5-4c38-bd7a-6b11f9b91dbc",
+            "PurchaseOrderId": "PO10237578",
+            "ContextId": "febb7b995791ba35::747e2d04f4e45723",
+            "LpnDetailId": "bc93a28c-47b9-4a44-a59a-d9635c5e32b3",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7598452326897334256
+                "PK": 7612504397293663157
             },
             "QuantityUomId": "Unit",
             "SeasonYear": null,
@@ -675,7 +675,7 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-10-07T13:57:25.587",
+            "UpdatedTimestamp": "2025-10-23T20:27:36.883",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
@@ -685,8 +685,8 @@
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7598452326917341956",
-            "Unique_Identifier": "7598452326917341956__f3bf349a-a5f5-4c38-bd7a-6b11f9b91dbc"
+            "PK": "7612504397703671408",
+            "Unique_Identifier": "7612504397703671408__bc93a28c-47b9-4a44-a59a-d9635c5e32b3"
         }
     ],
     "EntityLabels": null,
@@ -697,11 +697,11 @@
     "Length": null,
     "PreReceiptStatusId": "4",
     "SingleItemLpn": true,
-    "PurchaseOrderId": "PO10077686",
-    "ContextId": "30a8670c04a1196c::8aea6e974a4148a6",
+    "PurchaseOrderId": "PO10237578",
+    "ContextId": "0e3791c7523bb91a::ca800d0e92419b05",
     "Canceled": false,
-    "PK": "7598452326897334256",
-    "Unique_Identifier": "7598452326897334256__00V10072025QA3758700",
+    "PK": "7612504397293663157",
+    "Unique_Identifier": "7612504397293663157__00V10232025QA5520800",
     "DimensionUomId": null,
     "EstimationGroupId": null
 }</t>

--- a/J30/Output_files/iLPN_Information_Results.xlsx
+++ b/J30/Output_files/iLPN_Information_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,18 +504,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00V10232025QA5520800</t>
+          <t>00V11072025QA1452008</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1023QA3490</t>
+          <t>VGASN1107QA2830</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IN_VAS</t>
+          <t>MIXED_SKU</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>829747-091-S-T</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -557,7 +557,607 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO10237578</t>
+          <t>PO11073388</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>00V11072025QA1452008</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>24</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>PO11073388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00V11072025QA1481505</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FIRST_SKU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PO11075725</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00V11072025QA3998003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00V11072025QA5036804</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MEASUREMENT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>24</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00V11072025QA6618802</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>24</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00V11072025QA6969400</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>24</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>12</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00V11072025QA7682306</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PO11075725</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>12</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PO11073388</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>PO11073388</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00V11072025QA8085801</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
         </is>
       </c>
     </row>
@@ -587,7 +1187,7 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-10-23T20:13:59.729",
+    "CreatedTimestamp": "2025-11-07T20:02:01.182",
     "VolumeUomId": null,
     "PhysicalEntityCodeId": null,
     "FinalDestinationFacilityId": null,
@@ -600,7 +1200,7 @@
         "LpnWidth": 12.0
     },
     "DiversionCodeId": "IN_VAS",
-    "Process": "ReceivingLpnService",
+    "Process": "PreReceiptResponseProcessingService",
     "ItemAttributesValidated": true,
     "UpdatedBy": "vgana3",
     "LpnRequestedService": [],
@@ -610,18 +1210,18 @@
     "Width": null,
     "LpnSizeTypeId": "CARTON",
     "Asn": {
-        "AsnId": "VGASN1023QA3490"
+        "AsnId": "VGASN1107QA2830"
     },
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN1023QA3490",
-    "UpdatedTimestamp": "2025-10-23T20:29:54.3",
+    "AsnId": "VGASN1107QA2830",
+    "UpdatedTimestamp": "2025-11-07T20:26:00.444",
     "MarkFor": null,
     "CreatedBy": "vgana3",
     "ParentLpnId": null,
-    "LpnId": "00V10232025QA5520800",
+    "LpnId": "00V11072025QA8085801",
     "AllocationTypeId": "ProcessNeed And Sorting",
     "BusinessUnitId": null,
-    "LpnStatus": "4000",
+    "LpnStatus": "1000",
     "LocationId": null,
     "LpnTypeId": "ILPN",
     "AlternatePurchaseOrderId": null,
@@ -629,7 +1229,7 @@
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-10-23T20:13:59.771",
+            "CreatedTimestamp": "2025-11-07T20:02:01.183",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -640,7 +1240,7 @@
             "Process": "PreReceiptResponseProcessingService",
             "AsnLineId": null,
             "InventoryTypeId": null,
-            "ItemId": "DD9293-100-7",
+            "ItemId": "136027-115-9.5",
             "UpdatedBy": "vgana3",
             "InventoryAttribute1": "01000",
             "InventoryAttribute2": null,
@@ -654,16 +1254,16 @@
             "BusinessUnitId": null,
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
-            "PurchaseOrderId": "PO10237578",
-            "ContextId": "febb7b995791ba35::747e2d04f4e45723",
-            "LpnDetailId": "bc93a28c-47b9-4a44-a59a-d9635c5e32b3",
+            "PurchaseOrderId": "PO11072953",
+            "ContextId": "8ee44da44442ecb4::3fe0e2aa55513d92",
+            "LpnDetailId": "abc18c73-93e3-4e14-8a7e-fc8b43db5b85",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7612504397293663157
+                "PK": 7625457211826864172
             },
             "QuantityUomId": "Unit",
             "SeasonYear": null,
@@ -675,7 +1275,7 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-10-23T20:27:36.883",
+            "UpdatedTimestamp": "2025-11-07T20:26:00.526",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
@@ -685,8 +1285,8 @@
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7612504397703671408",
-            "Unique_Identifier": "7612504397703671408__bc93a28c-47b9-4a44-a59a-d9635c5e32b3"
+            "PK": "7625457211836876621",
+            "Unique_Identifier": "7625457211836876621__abc18c73-93e3-4e14-8a7e-fc8b43db5b85"
         }
     ],
     "EntityLabels": null,
@@ -695,13 +1295,13 @@
     "FacilityId": "1081",
     "Volume": null,
     "Length": null,
-    "PreReceiptStatusId": "4",
+    "PreReceiptStatusId": "3",
     "SingleItemLpn": true,
-    "PurchaseOrderId": "PO10237578",
-    "ContextId": "0e3791c7523bb91a::ca800d0e92419b05",
+    "PurchaseOrderId": "PO11072953",
+    "ContextId": "8ee44da44442ecb4::3fe0e2aa55513d92",
     "Canceled": false,
-    "PK": "7612504397293663157",
-    "Unique_Identifier": "7612504397293663157__00V10232025QA5520800",
+    "PK": "7625457211826864172",
+    "Unique_Identifier": "7625457211826864172__00V11072025QA8085801",
     "DimensionUomId": null,
     "EstimationGroupId": null
 }</t>

--- a/J30/Output_files/iLPN_Information_Results.xlsx
+++ b/J30/Output_files/iLPN_Information_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,18 +504,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00V11072025QA1452008</t>
+          <t>00V11132025QA5308300</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1107QA2830</t>
+          <t>VGASN1113QA7310</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>MEASUREMENT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>829747-091-S-T</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -557,25 +557,25 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO11073388</t>
+          <t>PO11137063</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00V11072025QA1452008</t>
+          <t>00V11132025QA8216301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1107QA2830</t>
+          <t>VGASN1113QA7310</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>STORAGE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>136027-115-9.5</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -617,547 +617,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PO11073388</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>00V11072025QA1481505</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>FIRST_SKU</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>829747-091-S-T</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>PO11075725</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00V11072025QA3998003</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>IN_VAS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>136027-115-9.5</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>24</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>PO11072953</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>00V11072025QA5036804</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MEASUREMENT</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>136027-115-9.5</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>24</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>12</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>PO11072953</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>00V11072025QA6618802</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>IN_VAS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>136027-115-9.5</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>24</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>PO11072953</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>00V11072025QA6969400</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IN_VAS</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>136027-115-9.5</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>24</v>
-      </c>
-      <c r="J8" t="n">
-        <v>12</v>
-      </c>
-      <c r="K8" t="n">
-        <v>12</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>PO11072953</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>00V11072025QA7682306</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>IN_VAS</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>829747-091-S-T</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>24</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12</v>
-      </c>
-      <c r="K9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>PO11075725</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>00V11072025QA7690607</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MIXED_SKU</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>829747-091-S-T</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>24</v>
-      </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
-      <c r="K10" t="n">
-        <v>12</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>PO11073388</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>00V11072025QA7690607</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MIXED_SKU</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>136027-115-9.5</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>24</v>
-      </c>
-      <c r="J11" t="n">
-        <v>12</v>
-      </c>
-      <c r="K11" t="n">
-        <v>12</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>PO11073388</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>00V11072025QA8085801</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>IN_VAS</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>136027-115-9.5</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>ProcessNeed And Sorting</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>PO11072953</t>
+          <t>PO11137063</t>
         </is>
       </c>
     </row>
@@ -1187,7 +647,7 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-11-07T20:02:01.182",
+    "CreatedTimestamp": "2025-11-14T00:48:18.841",
     "VolumeUomId": null,
     "PhysicalEntityCodeId": null,
     "FinalDestinationFacilityId": null,
@@ -1199,8 +659,8 @@
         "DestinationFacilityId": null,
         "LpnWidth": 12.0
     },
-    "DiversionCodeId": "IN_VAS",
-    "Process": "PreReceiptResponseProcessingService",
+    "DiversionCodeId": "STORAGE",
+    "Process": "ReceivingLpnService",
     "ItemAttributesValidated": true,
     "UpdatedBy": "vgana3",
     "LpnRequestedService": [],
@@ -1210,18 +670,18 @@
     "Width": null,
     "LpnSizeTypeId": "CARTON",
     "Asn": {
-        "AsnId": "VGASN1107QA2830"
+        "AsnId": "VGASN1113QA7310"
     },
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN1107QA2830",
-    "UpdatedTimestamp": "2025-11-07T20:26:00.444",
+    "AsnId": "VGASN1113QA7310",
+    "UpdatedTimestamp": "2025-11-14T00:57:57.44",
     "MarkFor": null,
     "CreatedBy": "vgana3",
     "ParentLpnId": null,
-    "LpnId": "00V11072025QA8085801",
+    "LpnId": "00V11132025QA8216301",
     "AllocationTypeId": "ProcessNeed And Sorting",
     "BusinessUnitId": null,
-    "LpnStatus": "1000",
+    "LpnStatus": "4000",
     "LocationId": null,
     "LpnTypeId": "ILPN",
     "AlternatePurchaseOrderId": null,
@@ -1229,7 +689,7 @@
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-11-07T20:02:01.183",
+            "CreatedTimestamp": "2025-11-14T00:48:18.841",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -1240,7 +700,7 @@
             "Process": "PreReceiptResponseProcessingService",
             "AsnLineId": null,
             "InventoryTypeId": null,
-            "ItemId": "136027-115-9.5",
+            "ItemId": "DD9293-100-7",
             "UpdatedBy": "vgana3",
             "InventoryAttribute1": "01000",
             "InventoryAttribute2": null,
@@ -1254,16 +714,16 @@
             "BusinessUnitId": null,
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
-            "PurchaseOrderId": "PO11072953",
-            "ContextId": "8ee44da44442ecb4::3fe0e2aa55513d92",
-            "LpnDetailId": "abc18c73-93e3-4e14-8a7e-fc8b43db5b85",
+            "PurchaseOrderId": "PO11137063",
+            "ContextId": "eb67f7dfb8565229::ce3dfe37726c749b",
+            "LpnDetailId": "095df8ad-5478-47a4-9e7d-cbde7a129968",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7625457211826864172
+                "PK": 7630812988417425175
             },
             "QuantityUomId": "Unit",
             "SeasonYear": null,
@@ -1275,7 +735,7 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-11-07T20:26:00.526",
+            "UpdatedTimestamp": "2025-11-14T00:56:24.49",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
@@ -1285,8 +745,8 @@
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7625457211836876621",
-            "Unique_Identifier": "7625457211836876621__abc18c73-93e3-4e14-8a7e-fc8b43db5b85"
+            "PK": "7630812988417437468",
+            "Unique_Identifier": "7630812988417437468__095df8ad-5478-47a4-9e7d-cbde7a129968"
         }
     ],
     "EntityLabels": null,
@@ -1295,13 +755,13 @@
     "FacilityId": "1081",
     "Volume": null,
     "Length": null,
-    "PreReceiptStatusId": "3",
+    "PreReceiptStatusId": "4",
     "SingleItemLpn": true,
-    "PurchaseOrderId": "PO11072953",
-    "ContextId": "8ee44da44442ecb4::3fe0e2aa55513d92",
+    "PurchaseOrderId": "PO11137063",
+    "ContextId": "f6e11a7233549102::5d4e101c84282b02",
     "Canceled": false,
-    "PK": "7625457211826864172",
-    "Unique_Identifier": "7625457211826864172__00V11072025QA8085801",
+    "PK": "7630812988417425175",
+    "Unique_Identifier": "7630812988417425175__00V11132025QA8216301",
     "DimensionUomId": null,
     "EstimationGroupId": null
 }</t>

--- a/J30/Output_files/iLPN_Information_Results.xlsx
+++ b/J30/Output_files/iLPN_Information_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,18 +504,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00V11132025QA5308300</t>
+          <t>00V11252025QA8409300</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1113QA7310</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MEASUREMENT</t>
+          <t>MIXED_SKU</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -557,25 +557,25 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO11137063</t>
+          <t>PO11255748</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00V11132025QA8216301</t>
+          <t>00V11252025QA8409300</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1113QA7310</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>MIXED_SKU</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -617,7 +617,127 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PO11137063</t>
+          <t>PO11255748</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00V11252025QA9579401</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PO11255748</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00V11252025QA9579401</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ProcessNeed And Sorting</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PO11255748</t>
         </is>
       </c>
     </row>
@@ -647,7 +767,7 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-11-14T00:48:18.841",
+    "CreatedTimestamp": "2025-11-26T01:03:48.932",
     "VolumeUomId": null,
     "PhysicalEntityCodeId": null,
     "FinalDestinationFacilityId": null,
@@ -659,7 +779,7 @@
         "DestinationFacilityId": null,
         "LpnWidth": 12.0
     },
-    "DiversionCodeId": "STORAGE",
+    "DiversionCodeId": "MIXED_SKU",
     "Process": "ReceivingLpnService",
     "ItemAttributesValidated": true,
     "UpdatedBy": "vgana3",
@@ -670,15 +790,15 @@
     "Width": null,
     "LpnSizeTypeId": "CARTON",
     "Asn": {
-        "AsnId": "VGASN1113QA7310"
+        "AsnId": "VGASN1125QA4410"
     },
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN1113QA7310",
-    "UpdatedTimestamp": "2025-11-14T00:57:57.44",
+    "AsnId": "VGASN1125QA4410",
+    "UpdatedTimestamp": "2025-11-26T01:05:31.839",
     "MarkFor": null,
     "CreatedBy": "vgana3",
     "ParentLpnId": null,
-    "LpnId": "00V11132025QA8216301",
+    "LpnId": "00V11252025QA9579401",
     "AllocationTypeId": "ProcessNeed And Sorting",
     "BusinessUnitId": null,
     "LpnStatus": "4000",
@@ -689,7 +809,7 @@
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-11-14T00:48:18.841",
+            "CreatedTimestamp": "2025-11-26T01:03:48.933",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -700,7 +820,7 @@
             "Process": "PreReceiptResponseProcessingService",
             "AsnLineId": null,
             "InventoryTypeId": null,
-            "ItemId": "DD9293-100-7",
+            "ItemId": "924156-100-S",
             "UpdatedBy": "vgana3",
             "InventoryAttribute1": "01000",
             "InventoryAttribute2": null,
@@ -714,16 +834,16 @@
             "BusinessUnitId": null,
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
-            "PurchaseOrderId": "PO11137063",
-            "ContextId": "eb67f7dfb8565229::ce3dfe37726c749b",
-            "LpnDetailId": "095df8ad-5478-47a4-9e7d-cbde7a129968",
+            "PurchaseOrderId": "PO11255748",
+            "ContextId": "57b80c3293402892::d85ec3f2abccf55e",
+            "LpnDetailId": "cc56ab87-782c-4cd3-93b8-0dcac7ef9b98",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7630812988417425175
+                "PK": 7641190289322284228
             },
             "QuantityUomId": "Unit",
             "SeasonYear": null,
@@ -735,7 +855,7 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-11-14T00:56:24.49",
+            "UpdatedTimestamp": "2025-11-26T01:03:59.708",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
@@ -745,8 +865,70 @@
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7630812988417437468",
-            "Unique_Identifier": "7630812988417437468__095df8ad-5478-47a4-9e7d-cbde7a129968"
+            "PK": "7641190289332292894",
+            "Unique_Identifier": "7641190289332292894__cc56ab87-782c-4cd3-93b8-0dcac7ef9b98"
+        },
+        {
+            "ExpiryDate": null,
+            "RetailPrice": null,
+            "CreatedTimestamp": "2025-11-26T01:03:48.933",
+            "Extended": {
+                "CutNumber": null,
+                "PurchaseOrderItemId": null,
+                "UnitOfMeasureCode": null,
+                "DeliveryNoteItemNumber": null
+            },
+            "CountryOfOrigin": "CN",
+            "Process": "PreReceiptResponseProcessingService",
+            "AsnLineId": null,
+            "InventoryTypeId": null,
+            "ItemId": "420420-420-M",
+            "UpdatedBy": "vgana3",
+            "InventoryAttribute1": "01000",
+            "InventoryAttribute2": null,
+            "InventoryAttribute3": null,
+            "InventoryAttribute4": null,
+            "PurgeDate": null,
+            "InventoryAttribute5": null,
+            "PurchaseOrderLineId": "",
+            "CreatedBy": "vgana3",
+            "BatchNumber": null,
+            "BusinessUnitId": null,
+            "StandardPackQuantity": null,
+            "ExternalOrderId": null,
+            "PurchaseOrderId": "PO11255748",
+            "ContextId": "57b80c3293402892::d85ec3f2abccf55e",
+            "LpnDetailId": "75f68e0c-46a3-4af9-9e2b-25ba92b93bbb",
+            "OriginalShippingFacilityId": null,
+            "StandardSubPackQuantity": null,
+            "VendorId": null,
+            "ExternalOrderLineId": null,
+            "LpnDetailStatus": "1000",
+            "Lpn": {
+                "PK": 7641190289322284228
+            },
+            "QuantityUomId": "Unit",
+            "SeasonYear": null,
+            "ManufacturingDate": null,
+            "Style": null,
+            "ProductClass": null,
+            "Season": null,
+            "CrossReferenceOrderId": null,
+            "HandlingUomQuantity": null,
+            "TierQuantity": null,
+            "CrossReferenceOrderLineId": null,
+            "UpdatedTimestamp": "2025-11-26T01:03:59.708",
+            "PrereceiptAllocatedQuantity": 0.0,
+            "LpnDetailAttribute": [],
+            "LpnDetailGroupingId": null,
+            "ShippedQuantity": 6.0,
+            "AlternatePurchaseOrderId": null,
+            "EntityLabels": null,
+            "ProductStatusId": null,
+            "OrgId": "1081",
+            "FacilityId": "1081",
+            "PK": "7641190289332304193",
+            "Unique_Identifier": "7641190289332304193__75f68e0c-46a3-4af9-9e2b-25ba92b93bbb"
         }
     ],
     "EntityLabels": null,
@@ -756,12 +938,12 @@
     "Volume": null,
     "Length": null,
     "PreReceiptStatusId": "4",
-    "SingleItemLpn": true,
-    "PurchaseOrderId": "PO11137063",
-    "ContextId": "f6e11a7233549102::5d4e101c84282b02",
+    "SingleItemLpn": false,
+    "PurchaseOrderId": "PO11255748",
+    "ContextId": "419a382080b1b226::f5937f8da593a2f1",
     "Canceled": false,
-    "PK": "7630812988417425175",
-    "Unique_Identifier": "7630812988417425175__00V11132025QA8216301",
+    "PK": "7641190289322284228",
+    "Unique_Identifier": "7641190289322284228__00V11252025QA9579401",
     "DimensionUomId": null,
     "EstimationGroupId": null
 }</t>

--- a/J30/Output_files/iLPN_Information_Results.xlsx
+++ b/J30/Output_files/iLPN_Information_Results.xlsx
@@ -504,13 +504,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00V11252025QA8409300</t>
+          <t>00V11262025QA2169401</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -557,20 +557,20 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO11255748</t>
+          <t>PO11266025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00V11252025QA8409300</t>
+          <t>00V11262025QA2169401</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -617,20 +617,20 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PO11255748</t>
+          <t>PO11266025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00V11252025QA9579401</t>
+          <t>00V11262025QA3029500</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -677,20 +677,20 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>PO11255748</t>
+          <t>PO11266025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00V11252025QA9579401</t>
+          <t>00V11262025QA3029500</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>PO11255748</t>
+          <t>PO11266025</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-11-26T01:03:48.932",
+    "CreatedTimestamp": "2025-11-26T18:31:05.356",
     "VolumeUomId": null,
     "PhysicalEntityCodeId": null,
     "FinalDestinationFacilityId": null,
@@ -790,15 +790,15 @@
     "Width": null,
     "LpnSizeTypeId": "CARTON",
     "Asn": {
-        "AsnId": "VGASN1125QA4410"
+        "AsnId": "VGASN1126QA8010"
     },
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN1125QA4410",
-    "UpdatedTimestamp": "2025-11-26T01:05:31.839",
+    "AsnId": "VGASN1126QA8010",
+    "UpdatedTimestamp": "2025-11-26T18:31:25.496",
     "MarkFor": null,
     "CreatedBy": "vgana3",
     "ParentLpnId": null,
-    "LpnId": "00V11252025QA9579401",
+    "LpnId": "00V11262025QA3029500",
     "AllocationTypeId": "ProcessNeed And Sorting",
     "BusinessUnitId": null,
     "LpnStatus": "4000",
@@ -809,7 +809,7 @@
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-11-26T01:03:48.933",
+            "CreatedTimestamp": "2025-11-26T18:31:05.385",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -834,16 +834,16 @@
             "BusinessUnitId": null,
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
-            "PurchaseOrderId": "PO11255748",
-            "ContextId": "57b80c3293402892::d85ec3f2abccf55e",
-            "LpnDetailId": "cc56ab87-782c-4cd3-93b8-0dcac7ef9b98",
+            "PurchaseOrderId": "PO11266025",
+            "ContextId": "b4f5e2e7051c1d27::f8479caa224415e9",
+            "LpnDetailId": "f53aebb9-3f0d-473b-858c-2d7b37626ead",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7641190289322284228
+                "PK": 7641818653562077535
             },
             "QuantityUomId": "Unit",
             "SeasonYear": null,
@@ -855,7 +855,7 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-11-26T01:03:59.708",
+            "UpdatedTimestamp": "2025-11-26T18:31:18.11",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
@@ -865,13 +865,13 @@
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7641190289332292894",
-            "Unique_Identifier": "7641190289332292894__cc56ab87-782c-4cd3-93b8-0dcac7ef9b98"
+            "PK": "7641818653852088664",
+            "Unique_Identifier": "7641818653852088664__f53aebb9-3f0d-473b-858c-2d7b37626ead"
         },
         {
             "ExpiryDate": null,
             "RetailPrice": null,
-            "CreatedTimestamp": "2025-11-26T01:03:48.933",
+            "CreatedTimestamp": "2025-11-26T18:31:05.41",
             "Extended": {
                 "CutNumber": null,
                 "PurchaseOrderItemId": null,
@@ -896,16 +896,16 @@
             "BusinessUnitId": null,
             "StandardPackQuantity": null,
             "ExternalOrderId": null,
-            "PurchaseOrderId": "PO11255748",
-            "ContextId": "57b80c3293402892::d85ec3f2abccf55e",
-            "LpnDetailId": "75f68e0c-46a3-4af9-9e2b-25ba92b93bbb",
+            "PurchaseOrderId": "PO11266025",
+            "ContextId": "b4f5e2e7051c1d27::f8479caa224415e9",
+            "LpnDetailId": "7e632824-095e-4d59-a155-20846113a75d",
             "OriginalShippingFacilityId": null,
             "StandardSubPackQuantity": null,
             "VendorId": null,
             "ExternalOrderLineId": null,
             "LpnDetailStatus": "1000",
             "Lpn": {
-                "PK": 7641190289322284228
+                "PK": 7641818653562077535
             },
             "QuantityUomId": "Unit",
             "SeasonYear": null,
@@ -917,7 +917,7 @@
             "HandlingUomQuantity": null,
             "TierQuantity": null,
             "CrossReferenceOrderLineId": null,
-            "UpdatedTimestamp": "2025-11-26T01:03:59.708",
+            "UpdatedTimestamp": "2025-11-26T18:31:18.115",
             "PrereceiptAllocatedQuantity": 0.0,
             "LpnDetailAttribute": [],
             "LpnDetailGroupingId": null,
@@ -927,8 +927,8 @@
             "ProductStatusId": null,
             "OrgId": "1081",
             "FacilityId": "1081",
-            "PK": "7641190289332304193",
-            "Unique_Identifier": "7641190289332304193__75f68e0c-46a3-4af9-9e2b-25ba92b93bbb"
+            "PK": "7641818654102091242",
+            "Unique_Identifier": "7641818654102091242__7e632824-095e-4d59-a155-20846113a75d"
         }
     ],
     "EntityLabels": null,
@@ -939,11 +939,11 @@
     "Length": null,
     "PreReceiptStatusId": "4",
     "SingleItemLpn": false,
-    "PurchaseOrderId": "PO11255748",
-    "ContextId": "419a382080b1b226::f5937f8da593a2f1",
+    "PurchaseOrderId": "PO11266025",
+    "ContextId": "940f407702268268::482b8939d00aae2",
     "Canceled": false,
-    "PK": "7641190289322284228",
-    "Unique_Identifier": "7641190289322284228__00V11252025QA9579401",
+    "PK": "7641818653562077535",
+    "Unique_Identifier": "7641818653562077535__00V11262025QA3029500",
     "DimensionUomId": null,
     "EstimationGroupId": null
 }</t>
